--- a/FIDELITY_Positions_Sep-04-2026.xlsx
+++ b/FIDELITY_Positions_Sep-04-2026.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alanl\GitHub\Stock_Picker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Alan/GitHub/Stock_Picker/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{33A30B0D-81A4-43BF-825C-3381433DCC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1728" yWindow="0" windowWidth="21312" windowHeight="12960" xr2:uid="{57F4BC12-09CD-42EC-8438-3EDE31333A23}"/>
+    <workbookView xWindow="1720" yWindow="600" windowWidth="21320" windowHeight="12960" xr2:uid="{57F4BC12-09CD-42EC-8438-3EDE31333A23}"/>
   </bookViews>
   <sheets>
     <sheet name="FIDELITY_Positions_Sep-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -736,16 +749,16 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1151,27 +1164,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D082F302-F94D-472D-9D90-B23F26017202}">
   <dimension ref="A1:P32"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.19921875" style="4" customWidth="1"/>
     <col min="2" max="2" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.375" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.75" customWidth="1"/>
-    <col min="8" max="8" width="11.25" customWidth="1"/>
-    <col min="9" max="9" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.125" customWidth="1"/>
-    <col min="16" max="16" width="6.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.3984375" customWidth="1"/>
+    <col min="5" max="5" width="9.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.796875" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" customWidth="1"/>
+    <col min="9" max="9" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.3984375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.19921875" customWidth="1"/>
+    <col min="16" max="16" width="6.3984375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1221,7 +1234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" s="14" t="s">
         <v>55</v>
       </c>
@@ -1241,7 +1254,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -1291,7 +1304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -1341,7 +1354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1391,7 +1404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -1441,7 +1454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
@@ -1491,7 +1504,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -1541,7 +1554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
@@ -1591,7 +1604,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -1641,7 +1654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
@@ -1691,7 +1704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
@@ -1741,7 +1754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1753,7 +1766,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A14" s="16"/>
       <c r="B14" s="16"/>
       <c r="C14" s="15"/>
@@ -1789,7 +1802,7 @@
       <c r="O14" s="19"/>
       <c r="P14" s="15"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1801,7 +1814,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" s="14" t="s">
         <v>56</v>
       </c>
@@ -1821,7 +1834,7 @@
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -1844,7 +1857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
@@ -1894,7 +1907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -1944,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>14</v>
       </c>
@@ -1994,7 +2007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>14</v>
       </c>
@@ -2044,7 +2057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>14</v>
       </c>
@@ -2094,7 +2107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>14</v>
       </c>
@@ -2144,7 +2157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>14</v>
       </c>
@@ -2194,7 +2207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -2206,7 +2219,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="15"/>
@@ -2242,7 +2255,7 @@
       <c r="O26" s="19"/>
       <c r="P26" s="15"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -2254,25 +2267,25 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" s="23"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" s="23"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" s="23"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" s="23"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="23" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J1:J13 J27:J1048576 J15:J25 L1:L1048576">
+  <conditionalFormatting sqref="J1:J13 L1:L1048576 J15:J25 J27:J1048576">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
